--- a/artfynd/A 32045-2025 artfynd.xlsx
+++ b/artfynd/A 32045-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1387,6 +1387,297 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126375103</v>
+      </c>
+      <c r="B9" t="n">
+        <v>75072</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Söder Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>480139</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6952431</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126375124</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Söder Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>480139</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6952435</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126375108</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91262</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Söder Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>480071</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6952395</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32045-2025 artfynd.xlsx
+++ b/artfynd/A 32045-2025 artfynd.xlsx
@@ -1392,7 +1392,7 @@
         <v>126375103</v>
       </c>
       <c r="B9" t="n">
-        <v>75072</v>
+        <v>75075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>126375124</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>126375108</v>
       </c>
       <c r="B11" t="n">
-        <v>91262</v>
+        <v>91265</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32045-2025 artfynd.xlsx
+++ b/artfynd/A 32045-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122154382</v>
+        <v>122172800</v>
       </c>
       <c r="B2" t="n">
-        <v>98154</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480179</v>
+        <v>480029</v>
       </c>
       <c r="R2" t="n">
-        <v>6952502</v>
+        <v>6952354</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122172819</v>
+        <v>122172799</v>
       </c>
       <c r="B3" t="n">
-        <v>90839</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480019</v>
+        <v>479934</v>
       </c>
       <c r="R3" t="n">
-        <v>6952359</v>
+        <v>6952347</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122172803</v>
+        <v>122172689</v>
       </c>
       <c r="B4" t="n">
-        <v>97191</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,7 +904,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480000</v>
+        <v>480033</v>
       </c>
       <c r="R4" t="n">
         <v>6952353</v>
@@ -949,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122172689</v>
+        <v>122172819</v>
       </c>
       <c r="B5" t="n">
-        <v>90835</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480033</v>
+        <v>480019</v>
       </c>
       <c r="R5" t="n">
-        <v>6952353</v>
+        <v>6952359</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1051,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122172800</v>
+        <v>126375108</v>
       </c>
       <c r="B6" t="n">
-        <v>95784</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,37 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Söder Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480029</v>
+        <v>480071</v>
       </c>
       <c r="R6" t="n">
-        <v>6952354</v>
+        <v>6952395</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,65 +1148,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122172799</v>
+        <v>126375124</v>
       </c>
       <c r="B7" t="n">
-        <v>91123</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Brynje, Jmt</t>
+          <t>Söder Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479934</v>
+        <v>480139</v>
       </c>
       <c r="R7" t="n">
-        <v>6952347</v>
+        <v>6952435</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,27 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122172802</v>
+        <v>122172804</v>
       </c>
       <c r="B8" t="n">
-        <v>57536</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480057</v>
+        <v>479976</v>
       </c>
       <c r="R8" t="n">
-        <v>6952365</v>
+        <v>6952297</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1392,7 +1357,7 @@
         <v>126375103</v>
       </c>
       <c r="B9" t="n">
-        <v>75075</v>
+        <v>83307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126375124</v>
+        <v>122172802</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1497,37 +1462,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Söder Brynje, Jmt</t>
+          <t>Brynje, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480139</v>
+        <v>480057</v>
       </c>
       <c r="R10" t="n">
-        <v>6952435</v>
+        <v>6952365</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1551,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1571,60 +1536,79 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126375108</v>
+        <v>127659920</v>
       </c>
       <c r="B11" t="n">
-        <v>91265</v>
+        <v>58817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>208249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Söder Brynje, Jmt</t>
+          <t>Tallmyrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480071</v>
+        <v>479778</v>
       </c>
       <c r="R11" t="n">
-        <v>6952395</v>
+        <v>6952652</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1648,12 +1632,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1668,15 +1652,209 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Johan Kjetselberg, Staffan Fridh</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122154382</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>480179</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6952502</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ward Tamsyn</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122172803</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Brynje, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>480000</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6952353</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
